--- a/output/미번역상품.xlsx
+++ b/output/미번역상품.xlsx
@@ -10,7 +10,7 @@
     <sheet name="미번역상품" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'미번역상품'!$A$1:$K$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'미번역상품'!$A$1:$K$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -549,12 +549,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>1215421243</t>
+          <t>1209198902</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>【選べる16・24枚】休足時間 ツボ刺激ジェルシート 足裏用 冷却 フットケア</t>
+          <t>シーボン ブライトベール UV プロテクター 40g SPF40 PA</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr"/>
@@ -565,28 +565,28 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>休足時間</t>
+          <t>C'BON</t>
         </is>
       </c>
       <c r="G2" s="7" t="n">
-        <v>2320</v>
+        <v>6000</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>바디/핸드/풋</t>
+          <t>UV케어</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>CHERRYSEOUL</t>
+          <t>qwelfare</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1215421243</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209198902</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1215224379</t>
+          <t>1163009734</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>さらさ 液体 無添加【大容量】1900g 植物由来の厳選成分配合 洗濯洗剤 詰め替え</t>
+          <t>【公式】ヘアボーテ エクラ ボタニカルエアカラーフォームEX ライトブラウン 150g ヘアカラー 泡 白髪染め 毛染め</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr"/>
@@ -612,14 +612,14 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>さらさ</t>
+          <t>ヘアボーテエクラ</t>
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>2694</v>
+        <v>8120</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>cococielshop</t>
+          <t>tamago-kichi</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1215224379</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1163009734</t>
         </is>
       </c>
     </row>
@@ -643,12 +643,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1094204441</t>
+          <t>1163009406</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>1+1 ナのシカフィリングジェル180ml 大容量/Gift付</t>
+          <t>【公式】ニューモ 育毛剤 3本セット</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr"/>
@@ -659,28 +659,28 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>アンジョ</t>
+          <t>ニューモ</t>
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>2700</v>
+        <v>23718</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>바디/핸드/풋</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Wiseholder</t>
+          <t>tamago-kichi</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1094204441</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1163009406</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>1214450849</t>
+          <t>967361211</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>PDRN デュアル ブースト 美容液ミスト【セラム90ml＋濃縮エッセンスタブレット2g セット】「ミスト美容液・ハリ・ツヤ・保湿・韓国コスメ」</t>
+          <t>ドクダミ ３種ヒアルロン酸デイリーフェイスマスクパック 5Weeks 5x7枚=35枚 ツヤケア</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr"/>
@@ -706,11 +706,11 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Tender garden</t>
+          <t>MITOMO</t>
         </is>
       </c>
       <c r="G5" s="7" t="n">
-        <v>3150</v>
+        <v>2500</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>0</v>
@@ -722,12 +722,12 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Tendergarden</t>
+          <t>yasumi</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214450849</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=967361211</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>1215233297</t>
+          <t>1215622852</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>【2個セット】PDRN クリームマスク 100ml 「植物由来PDRN・塗るパック・フェイスパック・洗い流すパック・クリームマスク・保湿パック・ハリ・ツヤケア・韓国コスメ」</t>
+          <t>【公式／話題の化粧下地】バブルプライマー / 毛穴カバー / 保湿 / トーンアップ / なめらか肌 / メイクノリUP / メイク崩れ防止 / プライマー / コスメ</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
@@ -753,11 +753,11 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Tender garden</t>
+          <t>AZTK</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
-        <v>4680</v>
+        <v>1490</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
@@ -769,12 +769,12 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Tendergarden</t>
+          <t>aztkjp</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1215233297</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1215622852</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>1214731496</t>
+          <t>1190164302</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>エッセンストナー化粧水 200ml 「PDRN・グルタチオン・パンテノール・保湿・高保湿・水光肌・韓国コスメ・韓国スキンケア」</t>
+          <t>ウルトラ D 30カプセル 飲む日焼け止め 次世代 UVケア 普通便</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
@@ -800,28 +800,28 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Tender garden</t>
+          <t>ヘリオケア</t>
         </is>
       </c>
       <c r="G7" s="7" t="n">
-        <v>2610</v>
+        <v>7980</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Tendergarden</t>
+          <t>dietclinic</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214731496</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1190164302</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>1214578555</t>
+          <t>1213037420</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>PDRN クリームマスク 100ml 「植物由来PDRN・塗るパック・フェイスパック・洗い流すパック・クリームマスク・保湿パック・ハリ・ツヤケア・韓国コスメ」</t>
+          <t>NMN エクトイン カタツムリ セラム 30ml</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr"/>
@@ -847,14 +847,14 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Tender garden</t>
+          <t>MY,BATHROOM</t>
         </is>
       </c>
       <c r="G8" s="7" t="n">
-        <v>2610</v>
+        <v>5496</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
@@ -863,12 +863,12 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Tendergarden</t>
+          <t>mybathroom</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214578555</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1213037420</t>
         </is>
       </c>
     </row>
@@ -878,12 +878,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1214576921</t>
+          <t>1193506615</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>PDRN クリームシートマスク 30g×5枚 「パック・エクソソーム・保湿・ハリ・ツヤケア・韓国コスメ」</t>
+          <t>【公式】FRAG.　フレグ パフュームヘアオイル No.2 ネロリインセンス 80ml 2本セット</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr"/>
@@ -894,28 +894,28 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Tender garden</t>
+          <t>FRAG.</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1620</v>
+        <v>5600</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Tendergarden</t>
+          <t>fragoffcial</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214576921</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1193506615</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>1134666076</t>
+          <t>1210866886</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>黒真珠エッセンスブラックマスク</t>
+          <t>[ANAZE] シルクフォームトリートメント ふんわり泡で毛先補修</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr"/>
@@ -941,28 +941,28 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>我的心機</t>
+          <t>ANAZE</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>935</v>
+        <v>2300</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>GPbeauty</t>
+          <t>anazeofficial</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1134666076</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210866886</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>1214971667</t>
+          <t>1203973048</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>[公式] ベータカーミング 24Hクリーム 50ml 保湿クリーム シカ ヒノキ水67% 高保湿 敏感肌 低刺激 ダーマコスメ 韓国スキンケア</t>
+          <t>シック Schick ボディ用 クアトロライト 2本入 使い捨てタイプ カミソリ</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
@@ -988,28 +988,28 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>LISSEDERM</t>
+          <t>Schick(シック)</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>4100</v>
+        <v>548</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>제모</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>lissederm</t>
+          <t>assetplan</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214971667</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203973048</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>1026840717</t>
+          <t>1207591325</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>セルローション　150ml　3本セット</t>
+          <t>スキンアクア(SKIN AQUA) トーンアップ UV エッセンス 日焼け止め 透明感 色白感UP ブルー 80g SPF50+ PA++++</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr"/>
@@ -1035,14 +1035,14 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>アルソア</t>
+          <t>ビオレu</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>12690</v>
+        <v>898</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>kyobi</t>
+          <t>assetplan</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1026840717</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207591325</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>1213893592</t>
+          <t>1204096455</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>【お試しセット】クイーンシルバー レフィル[枠練石けん] ＆ローション II</t>
+          <t>G9SKIN LACTO UYU ESSENCE UV CREAM 25g ホワイト トーンアップ 肌バリア SPF35 PA+++ 化粧下地</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr"/>
@@ -1082,28 +1082,28 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>アルソア</t>
+          <t>G9SKIN</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
-        <v>7500</v>
+        <v>980</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>UV케어</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>kyobi</t>
+          <t>assetplan</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1213893592</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204096455</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>1213893007</t>
+          <t>1179131970</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>【お試しセット】クイーンシルバー レフィル[枠練石けん] ＆セルローション</t>
+          <t>アクネ クリア スポット ソリューション 40ml 集中ケア 韓国コスメ</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr"/>
@@ -1129,11 +1129,11 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>アルソア</t>
+          <t>Atom美</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>8500</v>
+        <v>2831</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0</v>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>kyobi</t>
+          <t>moya09</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1213893007</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1179131970</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>1026840719</t>
+          <t>1159615664</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>クレイパック 100g</t>
+          <t>ダークスポットケア シミケアスノウコレクター 9.5ml 韓国コスメ</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
@@ -1176,14 +1176,14 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>アルソア</t>
+          <t>Atom美</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3120</v>
+        <v>3211</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>kyobi</t>
+          <t>moya09</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1026840719</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1159615664</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>1026840716</t>
+          <t>1165170078</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>セルローション　150ml</t>
+          <t>プロテイン インテンシブ シャンプー 400ml ダメージヘア 集中ケア 韓国コスメ</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr"/>
@@ -1223,28 +1223,28 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>アルソア</t>
+          <t>Atom美</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>4265</v>
+        <v>2831</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>kyobi</t>
+          <t>moya09</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1026840716</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1165170078</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>1192061380</t>
+          <t>1154419885</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>【話題の内外セット】青いアゼライン酸クリーム＆青いパントテン酸サプリ セットでお得</t>
+          <t>ヘア エッセンシャル オイル 100ml ダメージケア オイル 韓国コスメ</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr"/>
@@ -1270,28 +1270,28 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>brightdays</t>
+          <t>Atom美</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>6517</v>
+        <v>1757</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>brightdays</t>
+          <t>moya09</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1192061380</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1154419885</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>1207695414</t>
+          <t>1214581522</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>ペプチコア5 バイオセルロース 高密着シートマスク 4枚入り（1箱）</t>
+          <t>プライムアドバンサー ディエイジングスキンソフナー 5ml×30個 合計150ml 高保湿化粧水 ハリ・弾力・肌キメケア 韓国コスメ</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
@@ -1317,14 +1317,14 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>MLCL</t>
+          <t>オフィ</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>2400</v>
+        <v>2599</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>mlcl</t>
+          <t>kyo_market</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207695414</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214581522</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>1200118949</t>
+          <t>1211582248</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>【 -10℃クーリング効果！】エッセンシャル モデリングパック 皮膚科専売・業務用レベルの大容量 1kg</t>
+          <t>シークレットエッセンス 80ml＋30ml 企画セット 韓国コスメ 発酵エッセンス 保湿美容液 スキンケア エッセンス</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
@@ -1364,14 +1364,14 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>MLCL</t>
+          <t>sum37</t>
         </is>
       </c>
       <c r="G19" s="7" t="n">
-        <v>4880</v>
+        <v>7599</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>mlcl</t>
+          <t>kyo_market</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1200118949</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211582248</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>1214988890</t>
+          <t>1207091863</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>【夏のクーリングホームケア】エッセンシャル モデリングパック+アロエジェル セット</t>
+          <t>リードルショット フォーメン オールインワン100 Mプラス 150ml＋30ml 企画セット メンズスキンケア 韓国コスメ 化粧水 乳液 美容液</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
@@ -1411,28 +1411,28 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>MLCL</t>
+          <t>VTコスメティックス</t>
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>6790</v>
+        <v>3855</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>120000023</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>mlcl</t>
+          <t>kyo_market</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214988890</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207091863</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>1202632555</t>
+          <t>1210273263</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>【正規品・韓国皮膚科専用】 高保湿クリーム 200ml／敏感肌・乾燥肌向け・うるおいケア・しっとり保湿・韓国スキンケア・低刺激</t>
+          <t>コントロール-T クレンジングフォーム 200ml x2個 (+クレンジングフォーム 30ml) (贈呈品なくなり次第贈呈終了)</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr"/>
@@ -1458,14 +1458,14 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>MLCL</t>
+          <t>リアルバリア</t>
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>8000</v>
+        <v>5179</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>mlcl</t>
+          <t>gmarketplus</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202632555</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210273263</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>1110992833</t>
+          <t>1024564869</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>BATOXIN DERMA LIFT-UP SERUM</t>
+          <t>[1+1]ハニーアンドマカデミア ネイチャーシャンプー 500ml+プロテイントリートメント 500mlブラックベリーベイの香り 韓国シャンプー 保湿 ツヤ髪 ダメージケア カラーリング毛対応 ノンシ</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr"/>
@@ -1505,28 +1505,28 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>メディタイム</t>
+          <t>Kundal</t>
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>6980</v>
+        <v>3451</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>thelime</t>
+          <t>luckey_shop</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1110992833</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1024564869</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>1206847651</t>
+          <t>1186522406</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Aurelie オレリ- モイストオイル クレンジングウォーター 150g</t>
+          <t>【自然なトーン補正】 バーチ（水分）トーンアップ サンスクリーン 50mLデイリーUVケア・みずみずしい仕上がり</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1552,28 +1552,28 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Aurelie.</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="G23" s="7" t="n">
-        <v>3300</v>
+        <v>2799</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>UV케어</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>marketonsale</t>
+          <t>OliveYouth</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1206847651</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1186522406</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>1202533248</t>
+          <t>1107081017</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>日焼け止めクリーム Julies Lip ジュリスリップ</t>
+          <t>[1+1]ハイドロゲルパッチ3種セット:レチノール（しわケア）,ビタミンC（ブライトニング）,カフェイン（鎮静ケア)韓国コスメ</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -1599,28 +1599,28 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Julie's Lip</t>
+          <t>K-SECRET</t>
         </is>
       </c>
       <c r="G24" s="7" t="n">
-        <v>2970</v>
+        <v>3799</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>UV케어</t>
+          <t>스킨케어</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>hiclip</t>
+          <t>OliveYouth</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202533248</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1107081017</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>1214979012</t>
+          <t>1106986177</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>[fromrier 公式] EGFシカウォーターサンアンプル 56ml SPF50+PA++++ [ウォーター/マット] フロムリエ</t>
+          <t>タイムエナジークレンジングシート 50枚 / 韓国コスメ メイク落とし シート 拭き取り 洗顔 クレンジング 韓国</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
@@ -1646,28 +1646,28 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>fromrier</t>
+          <t>sum37</t>
         </is>
       </c>
       <c r="G25" s="7" t="n">
-        <v>3400</v>
+        <v>2397</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>UV케어</t>
+          <t>스킨케어</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>fromrier</t>
+          <t>OliveYouth</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214979012</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1106986177</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>1198051374</t>
+          <t>1210203177</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>マトメージュ まとめ髪スティッ ク スーパーホールド 13g アホ毛 前髪 固める ヘアワックス ウテ ナ</t>
+          <t>ホワイト ティー ピュア インダァルジャンス ボディ クリーム 400ml</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr"/>
@@ -1693,28 +1693,28 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>マトメージュ</t>
+          <t>エリザベスアーデン</t>
         </is>
       </c>
       <c r="G26" s="7" t="n">
-        <v>868</v>
+        <v>3130</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>헤어</t>
+          <t>바디/핸드/풋</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>tooh-sportech</t>
+          <t>easyworld</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1198051374</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210203177</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>1209048847</t>
+          <t>1210203189</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>タンタンコンクドロップ レフィル 55g TANN TANN CONC DROP つけ替え用 詰め替え スキンケア フェイスケア 保湿 うるおい</t>
+          <t>スージング クレンジングミルク 145ml</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr"/>
@@ -1740,11 +1740,11 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>デュウ</t>
+          <t>ドクターハウシュカ</t>
         </is>
       </c>
       <c r="G27" s="7" t="n">
-        <v>1999</v>
+        <v>3790</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0</v>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>world-depo</t>
+          <t>easyworld</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209048847</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210203189</t>
         </is>
       </c>
     </row>
@@ -1771,12 +1771,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>1209063604</t>
+          <t>1215036516</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>全ZEN シャンプー &amp;amp; コンディショナー セット 400ml x 2</t>
+          <t>ホワイトモス デオドラントスティック 75ml</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
@@ -1787,28 +1787,28 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Seika 全</t>
+          <t>アッカカッパ</t>
         </is>
       </c>
       <c r="G28" s="7" t="n">
-        <v>3798</v>
+        <v>3450</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>헤어</t>
+          <t>바디/핸드/풋</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>world-depo</t>
+          <t>easyworld</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209063604</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1215036516</t>
         </is>
       </c>
     </row>
@@ -1818,12 +1818,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>1204620083</t>
+          <t>1105982354</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>【ベタつきにくく・うるおい満たすコア保湿セラム】 デイリーハーモニー コアバランスセラム 30mL 韓国コスメ 保湿美容液 敏感肌 低刺激 乾燥肌 バリアケア</t>
+          <t>拱辰享(ゴンジンヒャン):雪 ホワイトエッセンス 45mL / くすみエッセンス 美容液 くすみ美容液 保湿エッセンス 韓国スキンケア 透明感アップ エイジング</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr"/>
@@ -1834,14 +1834,14 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>ELIBYTH</t>
+          <t>THE WHOO</t>
         </is>
       </c>
       <c r="G29" s="7" t="n">
-        <v>1980</v>
+        <v>9299</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>ELIBYTH</t>
+          <t>ParkGunShop</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204620083</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1105982354</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>1176904428</t>
+          <t>1170729506</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>【公式】ELIFIT エリフィット ブリリアントパック　フェイスパック 韓国コスメ 保湿ケア 個別包装　10枚入り シートマスク 乾燥肌ケア 韓国マスク</t>
+          <t>[公式/日本国内発送] ［なりたい肌で選ぶセット］パック シートマスク グルタチオン PDRN 美容針 リズム RISM ベース デイリーケアマスク4袋＋ピコレーザー ニードルスポットパック1袋</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
@@ -1881,11 +1881,11 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>DANCING WHALE</t>
+          <t>RISM</t>
         </is>
       </c>
       <c r="G30" s="7" t="n">
-        <v>3080</v>
+        <v>4070</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0</v>
@@ -1897,12 +1897,12 @@
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>dancingwhaleOfficial</t>
+          <t>rism-official</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1176904428</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1170729506</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>1176847022</t>
+          <t>1200554723</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>【公式】ウルトラシカパック10枚入り　ダメージ肌・敏感肌向け　敏感肌にも優しい使い心地　日焼け　個別包装</t>
+          <t>スターダストグロウエッセンス</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
@@ -1928,14 +1928,14 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>DANCING WHALE</t>
+          <t>ココスター</t>
         </is>
       </c>
       <c r="G31" s="7" t="n">
-        <v>3080</v>
+        <v>1320</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>dancingwhaleOfficial</t>
+          <t>kocostar</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1176847022</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1200554723</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>1030176518</t>
+          <t>1212733705</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>リープロ　ICR 3D セーブローション 300ml　全身用化粧水</t>
+          <t>【ULTOWA】ウルトワ INITIAL SERIESイニシャルシリーズ GRAVITY LOG グラビティログコンディショナー　400ml しっとりヘアコンディショナー GRAVITY</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
@@ -1975,28 +1975,28 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>ReePRO</t>
+          <t>ULTOWA</t>
         </is>
       </c>
       <c r="G32" s="7" t="n">
-        <v>6380</v>
+        <v>5600</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>espritnet</t>
+          <t>tinder</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1030176518</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212733705</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>894512201</t>
+          <t>1212733508</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>ココルタン　ココルタン　モイストクリーム 100g 全身保湿クリーム　敏感肌乾燥肌</t>
+          <t>【ULTOWA】ウルトワ INITIAL SERIESイニシャルシリーズ GRAVITY LOG グラビティログシャンプー　400ml しっとりヘアシャンプー GRAVITY LOG</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
@@ -2022,28 +2022,28 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>ココルタン</t>
+          <t>ULTOWA</t>
         </is>
       </c>
       <c r="G33" s="7" t="n">
-        <v>8800</v>
+        <v>5600</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>espritnet</t>
+          <t>tinder</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=894512201</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212733508</t>
         </is>
       </c>
     </row>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>982038140</t>
+          <t>1212735720</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Beauche moisturizing cream enriched with Vitamin E 30g</t>
+          <t>【ULTOWA】ウルトワ INITIAL SERIESイニシャルシリーズ PLASMA SILICA プラズマシリカコンディショナー　400ml さらさらヘアコンディショナー</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
@@ -2069,28 +2069,28 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Beauche Beauty</t>
+          <t>ULTOWA</t>
         </is>
       </c>
       <c r="G34" s="7" t="n">
-        <v>1890</v>
+        <v>5600</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>바디/핸드/풋</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>clarkshopping</t>
+          <t>tinder</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=982038140</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212735720</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>1077798291</t>
+          <t>1212733956</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>【公式】コンディショナー バー ザ ガーディアン 60ｇ/ノンシリコン/固形コンディショナー/エシカル/ヴィーガン/頭皮ケア/髪質改善</t>
+          <t>【ULTOWA】ウルトワ INITIAL SERIESイニシャルシリーズ PLASMA SILICA プラズマシリカシャンプー　400ml さらさらヘアシャンプー PLASMA SILICA</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
@@ -2116,14 +2116,14 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>エティーク</t>
+          <t>ULTOWA</t>
         </is>
       </c>
       <c r="G35" s="7" t="n">
-        <v>1386</v>
+        <v>5600</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
@@ -2132,12 +2132,12 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>favostyle</t>
+          <t>tinder</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1077798291</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212733956</t>
         </is>
       </c>
     </row>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>1077798290</t>
+          <t>1168160315</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>【公式】コンディショナー バー ワンダーバー 60ｇ</t>
+          <t>リケラエマルジョン　リトルサイエンティスト　詰め替え1000ｇ</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr"/>
@@ -2163,11 +2163,11 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>エティーク</t>
+          <t>リトルサイエンティスト</t>
         </is>
       </c>
       <c r="G36" s="7" t="n">
-        <v>1386</v>
+        <v>17600</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>5</v>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>favostyle</t>
+          <t>tinder</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1077798290</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1168160315</t>
         </is>
       </c>
     </row>
@@ -2194,12 +2194,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>1183037325</t>
+          <t>1056271356</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>フォーデイズ　ムーサ イオ DN リッチ クリーム final</t>
+          <t>マイハニー ザハニーオイルブレス 80ml ヘアオイル Hオイルブレス</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
@@ -2210,28 +2210,28 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>フォーデイズ</t>
+          <t>マイハニーレメディー</t>
         </is>
       </c>
       <c r="G37" s="7" t="n">
-        <v>3480</v>
+        <v>4280</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>39market</t>
+          <t>cosme-fines</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1183037325</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1056271356</t>
         </is>
       </c>
     </row>
@@ -2241,12 +2241,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>1049528532</t>
+          <t>1203606043</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>クレンジングバーム 100g</t>
+          <t>【トライアルセット6種組】シャンプートリートメントセット(バスグロウ3種/スーパーリッチクリスタル3種）6種各1枚 お試しサシェ6回分10mL+10mL 携帯用 旅行用</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr"/>
@@ -2257,28 +2257,28 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>ノエビア</t>
+          <t>ラックス</t>
         </is>
       </c>
       <c r="G38" s="7" t="n">
-        <v>5980</v>
+        <v>860</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>total-item-shop</t>
+          <t>seaable</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1049528532</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203606043</t>
         </is>
       </c>
     </row>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>1214609928</t>
+          <t>1150799106</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>EC限定 VC100エッセンスローションEX 285mL＋VC100 エマルジョン EXパウチ ドクターシーラボビタミンC 化粧水 ポンプタイプ</t>
+          <t>MDSKIN LABO シートマスク パック アゼライン酸 ビタミンC誘導体 グリチルリチン酸ジカリウム セラミド フェイスマスク フェイスパック オールインワン</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr"/>
@@ -2304,14 +2304,14 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>ドクターシーラボ</t>
+          <t>MDSKIN LABO</t>
         </is>
       </c>
       <c r="G39" s="7" t="n">
-        <v>8910</v>
+        <v>800</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>drci-labo</t>
+          <t>nporder</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214609928</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1150799106</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>1214938418</t>
+          <t>1089747800</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>[角質ケア] セラディクス トリプルレチノールウォッシュピール, 30ml, 角質ケア 毛穴ケア 導入美容液 ピーリング 韓国スキンケア</t>
+          <t>ellips ヘアオイル シャイニーブラック(ピーチ＆シトラスの香り)50粒入 正規品 洗い流さないトリートメント ヘアビタミン 保湿 持ち運び ハリ コシ 潤い ツヤ 黒髪</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr"/>
@@ -2351,28 +2351,28 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>セラディックス</t>
+          <t>エリップス</t>
         </is>
       </c>
       <c r="G40" s="7" t="n">
-        <v>4621</v>
+        <v>1980</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>kiki_shop</t>
+          <t>crossplus</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214938418</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1089747800</t>
         </is>
       </c>
     </row>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>1214886234</t>
+          <t>1089750324</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>ミネラルリスト ラスティング アイライナ # ダイヤモンド 0.35g</t>
+          <t>ellips ヘアオイル レディシャイニー(スウィートフローラルブーケの香り)50粒入 日本限定 正規品 洗い流さないトリートメント 保湿 持ち運び ハリ コシ 切毛 枝毛 ダメージケア ツヤ</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr"/>
@@ -2398,28 +2398,28 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>ベアミネラル</t>
+          <t>エリップス</t>
         </is>
       </c>
       <c r="G41" s="7" t="n">
-        <v>2510</v>
+        <v>1980</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>coscora</t>
+          <t>crossplus</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214886234</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1089750324</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>1214886256</t>
+          <t>1089173212</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>メンズ制汗ロルオン 50ml</t>
+          <t>ellips ヘアオイル スムース&amp;amp;シャイニー(トロピカルフルーツの香り)50粒入 正規品 洗い流さないトリートメント ヘアビタミン サラサラ 持ち運び ダメージケア 保湿 潤い</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr"/>
@@ -2445,28 +2445,28 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>クラランス</t>
+          <t>エリップス</t>
         </is>
       </c>
       <c r="G42" s="7" t="n">
-        <v>3240</v>
+        <v>1980</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>120000023</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>coscora</t>
+          <t>crossplus</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214886256</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1089173212</t>
         </is>
       </c>
     </row>
@@ -2476,12 +2476,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>1188543576</t>
+          <t>1192459180</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>センスローション 美肌ケア 引き締め　150ml</t>
+          <t>VT PDRN リードルショット ブラシ ヘアセラム 100ml （頭皮マッサージ一体型・PDRN配合・スカルプケア美容液）頭皮ケア スカルプ美容液 ブラシタイプ PDRN配合 頭皮マッサージ ベタつ</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr"/>
@@ -2492,28 +2492,28 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>ルクセア</t>
+          <t>VTコスメティックス</t>
         </is>
       </c>
       <c r="G43" s="7" t="n">
-        <v>2448</v>
+        <v>5140</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>120000023</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>luxcear</t>
+          <t>TokimekiBox</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188543576</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1192459180</t>
         </is>
       </c>
     </row>
@@ -2523,12 +2523,12 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>1199807022</t>
+          <t>1207202992</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>SHINY CICA 炭酸水 クレンジングフォーム 正規販売店 韓国コスメ 韓国化粧品 美肌 済州島 クレンザー スキンケア 素肌 高密度</t>
+          <t>【公式】SILK THE RICH ボディウォッシュ [単品]</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr"/>
@@ -2539,28 +2539,28 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>SHINY Cosmetic</t>
+          <t>SILK THE RICH</t>
         </is>
       </c>
       <c r="G44" s="7" t="n">
-        <v>3245</v>
+        <v>1760</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>kiyose-store</t>
+          <t>silktherich</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1199807022</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1207202992</t>
         </is>
       </c>
     </row>
@@ -2570,12 +2570,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>1201206332</t>
+          <t>1204628546</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>【LIVNA公式】チャプター１パーフェクトライスバリアリペアクリーム 60ml（肌バリア 鎮静 ゆらぎ肌 ヒアルロン酸 エラスチン）</t>
+          <t>【公式】SILK THE RICH シャンプー・トリートメント・ヘアオイル３点セット</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr"/>
@@ -2586,28 +2586,28 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>LIVNA</t>
+          <t>SILK THE RICH</t>
         </is>
       </c>
       <c r="G45" s="7" t="n">
-        <v>3300</v>
+        <v>6380</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>livna_official</t>
+          <t>silktherich</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1201206332</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1204628546</t>
         </is>
       </c>
     </row>
@@ -2617,12 +2617,12 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>1201206101</t>
+          <t>1202143695</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>【LIVNA公式】チャプター３バランスハトムギマルチ水分鎮静クリーム60ml（肌荒れ ニキビ 赤み トラブル 鎮静 シカ）</t>
+          <t>[NEW][1+1] 3番 ふんわり毛穴ケアセラム 30ml</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr"/>
@@ -2633,14 +2633,14 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>LIVNA</t>
+          <t>ナンバーズイン</t>
         </is>
       </c>
       <c r="G46" s="7" t="n">
-        <v>2900</v>
+        <v>3630</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
@@ -2649,12 +2649,12 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>livna_official</t>
+          <t>LMG</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1201206101</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202143695</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>1201206035</t>
+          <t>1202138394</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>【LIVNA公式】チャプター３バランスハトムギマルチ鎮静アンプル30ml（肌荒れ ニキビ 赤み トラブル 鎮静 シカ 美容液）</t>
+          <t>[NEW] 3番 陶器結 トーンアップベージュ サンスクリーン 50ml 2種（ブラー/グロウ）</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr"/>
@@ -2680,28 +2680,28 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>LIVNA</t>
+          <t>ナンバーズイン</t>
         </is>
       </c>
       <c r="G47" s="7" t="n">
-        <v>2900</v>
+        <v>2450</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>UV케어</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>livna_official</t>
+          <t>LMG</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1201206035</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1202138394</t>
         </is>
       </c>
     </row>
@@ -2711,12 +2711,12 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>1214754750</t>
+          <t>1078324428</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>アボカド オアシス モイスチャークリーム 大容量（保湿バリアケア）320g</t>
+          <t>ダーマトリー リニューアルシカガーゼパッド 80枚（水分/鎮静）</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr"/>
@@ -2727,11 +2727,11 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>ピュアメロウ</t>
+          <t>ダーマトリー</t>
         </is>
       </c>
       <c r="G48" s="7" t="n">
-        <v>1770</v>
+        <v>3298</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
@@ -2743,12 +2743,12 @@
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>puremellow</t>
+          <t>andanteya</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214754750</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1078324428</t>
         </is>
       </c>
     </row>
@@ -2758,12 +2758,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>1212713151</t>
+          <t>1198522428</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>【NERITIA公式】セラムサンクリーム35ml / 日焼け止め / 下地 / ベースメイク / 日焼け止めクリーム / BBクリーム / スキンケア</t>
+          <t>オーバーナイト リップマスク 20ml 4種ビタ グレーズド レモンシュガー スクラブ コラーゲンブースト ミントクーリング</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr"/>
@@ -2774,28 +2774,28 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>NERITIA</t>
+          <t>TOCOBO</t>
         </is>
       </c>
       <c r="G49" s="7" t="n">
-        <v>2980</v>
+        <v>3180</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>UV케어</t>
+          <t>스킨케어</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>fillgrow</t>
+          <t>andanteya</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212713151</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1198522428</t>
         </is>
       </c>
     </row>
@@ -2805,12 +2805,12 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>1215180645</t>
+          <t>1198519250</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>RIMAN ブースター＋セラム＋クリーム＋ミスト＋カーミングジェル 5種セット 基礎化粧品 潤い 艶肌 鎮静</t>
+          <t>ミニサンスティック 11g 3種キーリングプレゼント ミニシカ ミニビタ ミニコットン</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr"/>
@@ -2821,28 +2821,28 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>インセルダーム</t>
+          <t>TOCOBO</t>
         </is>
       </c>
       <c r="G50" s="7" t="n">
-        <v>27270</v>
+        <v>1980</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>UV케어</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>seoulplus</t>
+          <t>andanteya</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1215180645</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1198519250</t>
         </is>
       </c>
     </row>
@@ -2852,12 +2852,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>1215121855</t>
+          <t>1172106877</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>RENECELLリトークマスク65ml</t>
+          <t>ジークップ ケアセラ エコアスノウ 硫黄石鹸 (4個入)</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr"/>
@@ -2868,11 +2868,11 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>ルネセル</t>
+          <t>ケアセラ</t>
         </is>
       </c>
       <c r="G51" s="7" t="n">
-        <v>1515</v>
+        <v>3710</v>
       </c>
       <c r="H51" s="3" t="n">
         <v>0</v>
@@ -2884,12 +2884,12 @@
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>seoulplus</t>
+          <t>KOREAMALL1</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1215121855</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1172106877</t>
         </is>
       </c>
     </row>
@@ -2899,12 +2899,12 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>1215052508</t>
+          <t>1172104844</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>RENECELLダイヤモンドフィルセット(no box)</t>
+          <t>（圧倒的な購入レビュー）NTH クイーンズヘナ 染毛剤 ヘナ ニューブラウン 100g（染毛具提供）</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr"/>
@@ -2915,28 +2915,28 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>ルネセル</t>
+          <t>Nth Degree</t>
         </is>
       </c>
       <c r="G52" s="7" t="n">
-        <v>12650</v>
+        <v>3800</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>seoulplus</t>
+          <t>KOREAMALL1</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1215052508</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1172104844</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2946,12 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>1215042961</t>
+          <t>1205562577</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>RENECELLリカバリーセラム30ml</t>
+          <t>エンジョイ オールラウンド エアリー サンクッション EX 25g</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr"/>
@@ -2962,28 +2962,28 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>ルネセル</t>
+          <t>サイニック</t>
         </is>
       </c>
       <c r="G53" s="7" t="n">
-        <v>4315</v>
+        <v>2568</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>UV케어</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>seoulplus</t>
+          <t>markets7</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1215042961</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1205562577</t>
         </is>
       </c>
     </row>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>1203824462</t>
+          <t>1205564469</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>RIMAN ザマトロジークリーム50ml</t>
+          <t>レチノール 500IU セラム, 30ml</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr"/>
@@ -3009,11 +3009,11 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>インセルダーム</t>
+          <t>BONCEPT</t>
         </is>
       </c>
       <c r="G54" s="7" t="n">
-        <v>8076</v>
+        <v>1683</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0</v>
@@ -3025,12 +3025,12 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>seoulplus</t>
+          <t>markets7</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1203824462</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1205564469</t>
         </is>
       </c>
     </row>
@@ -3040,12 +3040,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>1109780951</t>
+          <t>1148824099</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>5個 ECM物質に着目した ヒト幹細胞 美容液 5日間プレミアムケア ACクリスタルソリューション 使い切り パウチ 1mL 無香料 日本製 エイジングケア EGF 小分け 個包装</t>
+          <t>【20%OFF 全ブランド跨ぎ割引】 イロン 当帰 トナー 500ml+マスクパックをプレゼント</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr"/>
@@ -3056,14 +3056,14 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>MiRaMiRa</t>
+          <t>ILLON</t>
         </is>
       </c>
       <c r="G55" s="7" t="n">
-        <v>980</v>
+        <v>7790</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
@@ -3072,12 +3072,12 @@
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>miramira</t>
+          <t>HappyBGLD</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1109780951</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1148824099</t>
         </is>
       </c>
     </row>
@@ -3087,12 +3087,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>989280834</t>
+          <t>1102128974</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>【訳あり】60個 ECM物質に着目した ヒト幹細胞 美容液 60日継続ケア ACクリスタルソリューション 使い切り パウチ 1mL 無香料 日本製 エイジングケア EGF 小分け 個包装</t>
+          <t>【20%OFF 全ブランド跨ぎ割引】ボラヨン ヒアロテン パウダー(水分/鎮静) クーリングモデリングパック 500g+パック道具+ マスクパック追加贈呈</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr"/>
@@ -3103,14 +3103,14 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>MiRaMiRa</t>
+          <t>volayon</t>
         </is>
       </c>
       <c r="G56" s="7" t="n">
-        <v>5983</v>
+        <v>4199</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>miramira</t>
+          <t>HappyBGLD</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=989280834</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1102128974</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>1087980274</t>
+          <t>1211561315</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>ディアテック ウクワ UKUWA モイストプラス 100g【3個セット】</t>
+          <t>【20%OFF 全ブランド跨ぎ割引】油水分バランスパッケージ / スキャルプシャンプー 500ml + ブラックトリートメント 500ml +マスクパックをプレゼント</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr"/>
@@ -3150,14 +3150,14 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>ディアテック</t>
+          <t>KEMA</t>
         </is>
       </c>
       <c r="G57" s="7" t="n">
-        <v>4500</v>
+        <v>13890</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
@@ -3166,12 +3166,12 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>carabeautyconcierge</t>
+          <t>HappyBGLD</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1087980274</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211561315</t>
         </is>
       </c>
     </row>
@@ -3181,12 +3181,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>1087980242</t>
+          <t>1211067492</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>ディアテック ウクワ UKUWA モイストプラス 100g　【2個セット】</t>
+          <t>【20%OFF 全ブランド跨ぎ割引】スキンボリック ゴールドカプセル 100ml 高濃度の保湿ハリシワ改善アンプル+マスクパックをプレゼント</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr"/>
@@ -3197,28 +3197,28 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>ディアテック</t>
+          <t>SKINBOLIC</t>
         </is>
       </c>
       <c r="G58" s="7" t="n">
-        <v>3300</v>
+        <v>19100</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>헤어</t>
+          <t>스킨케어</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>carabeautyconcierge</t>
+          <t>HappyBGLD</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1087980242</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211067492</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>1209393511</t>
+          <t>1210939334</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>オーオイル モイスト リフィル 500ml 詰め替え用 ヘアオイル ボディオイル スキンオイル ローズ 天然精油</t>
+          <t>【20%OFF 全ブランド跨ぎ割引】オルソミンC ルミジアンプル (15ml) 40% 高濃度の純粋ビタミンCを含有+マスクパックをプレゼント</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr"/>
@@ -3244,28 +3244,28 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>O skin &amp;amp; hair</t>
+          <t>VEMONTES</t>
         </is>
       </c>
       <c r="G59" s="7" t="n">
-        <v>14800</v>
+        <v>5790</v>
       </c>
       <c r="H59" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>헤어</t>
+          <t>스킨케어</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>serendipity2</t>
+          <t>HappyBGLD</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209393511</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210939334</t>
         </is>
       </c>
     </row>
@@ -3275,12 +3275,12 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>1194283472</t>
+          <t>1168247824</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>ケアセラ(CareCera) APフェイス&amp;amp;ボディ 乳液 200ml (セラミドプラス×8種の天然型セラミド配合)</t>
+          <t>チョンギダン ファヒョン バランサー 5ml×30個 韓方化粧水 高保湿 ハリ ツヤ 個包装 韓国コスメ サンプル</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr"/>
@@ -3291,28 +3291,28 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>ケアセラ</t>
+          <t>THE WHOO</t>
         </is>
       </c>
       <c r="G60" s="7" t="n">
-        <v>864</v>
+        <v>2009</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>바디/핸드/풋</t>
+          <t>스킨케어</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>bequemstore</t>
+          <t>manmulsang</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1194283472</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1168247824</t>
         </is>
       </c>
     </row>
@@ -3322,12 +3322,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>1194288393</t>
+          <t>1123203922</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>セザンヌ マスカラリムーバー 5.0g 頑固なマスカラもするんと落とす 幅広コーム</t>
+          <t>【大容量セット】[1+1]カラーフィット ヘアシャンプー 1000ml/トリートメント1000ml カラーケア用 韓国ヘアケア 毎日使える ダメージ補修 保湿 ツヤ髪ケア</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr"/>
@@ -3338,28 +3338,28 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>セザンヌ</t>
+          <t>LODEURLETTE</t>
         </is>
       </c>
       <c r="G61" s="7" t="n">
-        <v>597</v>
+        <v>4694</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>bequemstore</t>
+          <t>manmulsang</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1194288393</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1123203922</t>
         </is>
       </c>
     </row>
@@ -3369,12 +3369,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>1179610392</t>
+          <t>1106987513</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>舞妓フェイスウオッシュ</t>
+          <t>[1+1]タイムエナジーリセッティングトナー170mL / エマルジョン120mL 化粧水・乳液セット 保湿・ハリ・ツヤケア 韓国スキンケア</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr"/>
@@ -3385,11 +3385,11 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>AISHODO</t>
+          <t>sum37</t>
         </is>
       </c>
       <c r="G62" s="7" t="n">
-        <v>950</v>
+        <v>5901</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>0</v>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>aishodo</t>
+          <t>manmulsang</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1179610392</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1106987513</t>
         </is>
       </c>
     </row>
@@ -3416,12 +3416,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>1182343949</t>
+          <t>1081525647</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>エッセンスクレンジングジェル （135g）　ヒアルロン酸　ジヒドロキシプロピルアルギニンHCI　米発酵液</t>
+          <t>拱辰享フォーム クレンザー 2ml 120個 韓国コスメ 洗顔フォーム 個包装 サンプル パウチ 旅行用 スキンケア</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr"/>
@@ -3432,14 +3432,14 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>RICE UP SKIN</t>
+          <t>THE WHOO</t>
         </is>
       </c>
       <c r="G63" s="7" t="n">
-        <v>2200</v>
+        <v>2161</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
@@ -3448,12 +3448,12 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>bijinnuka</t>
+          <t>manmulsang</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1182343949</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1081525647</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>1053474210</t>
+          <t>1212873959</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>SilkyWax ブラジリアンワックス ペーパー 100枚 ワックス 脱毛 ストリップス ストリップスペーパー セルフ 自宅</t>
+          <t>フォリゲン シックニング スカルプトニック 120ml 2個 韓国頭皮ケア 髪のハリコシケア ボリューム感ケア</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr"/>
@@ -3479,28 +3479,28 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Silky Wax</t>
+          <t>Dr.FORHAIR</t>
         </is>
       </c>
       <c r="G64" s="7" t="n">
-        <v>678</v>
+        <v>4299</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>제모</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>SilkyWax</t>
+          <t>refill</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1053474210</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212873959</t>
         </is>
       </c>
     </row>
@@ -3510,12 +3510,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>1160008640</t>
+          <t>1212719705</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>ブラジリアンワックス 450g スターターセット ペーパー スパチュラ シュガーワックス ワックス脱毛 脱毛器 全身 脱毛 VIO脱毛 純国産無添加</t>
+          <t>グルタハイヤ セラム ボディローション フローレスブライト 300ml 韓国ボディケア 保湿ローション 明るいツヤ肌印象</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr"/>
@@ -3526,28 +3526,28 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Silky Wax</t>
+          <t>ヴァセリン</t>
         </is>
       </c>
       <c r="G65" s="7" t="n">
-        <v>2980</v>
+        <v>1950</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>제모</t>
+          <t>바디/핸드/풋</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>SilkyWax</t>
+          <t>refill</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1160008640</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212719705</t>
         </is>
       </c>
     </row>
@@ -3557,12 +3557,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>1160008478</t>
+          <t>1212719275</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>【純国産/大容量450g】 シュガーワックス 単品 ブラジリアンワックス VIO 全身 脱毛 無添加 水で洗い流せる デリケートゾーン</t>
+          <t>グルタハイヤ セラム ボディローション プロエイジリストア 300ml 韓国ボディケア 保湿ローション しっとりハリツヤ肌印象</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr"/>
@@ -3573,28 +3573,28 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Silky Wax</t>
+          <t>ヴァセリン</t>
         </is>
       </c>
       <c r="G66" s="7" t="n">
-        <v>2480</v>
+        <v>1950</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>제모</t>
+          <t>바디/핸드/풋</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>SilkyWax</t>
+          <t>refill</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1160008478</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212719275</t>
         </is>
       </c>
     </row>
@@ -3604,12 +3604,12 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>1113303393</t>
+          <t>1097757129</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>ブラジリアンワックス　鼻毛ワックス脱毛キット 3回分 ストッパー付 メンズ 男性 女性 鼻毛処理 レディース 鼻毛取り 自宅 セルフ 鼻毛脱毛キット</t>
+          <t>名品スペシャルシャンプー企画[500ml+145ml]毛髪集中ケア韓国シャンプー ダメージケア 保湿 ツヤ</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr"/>
@@ -3620,28 +3620,28 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Silky Wax</t>
+          <t>デンギモリ</t>
         </is>
       </c>
       <c r="G67" s="7" t="n">
-        <v>580</v>
+        <v>3600</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>제모</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>SilkyWax</t>
+          <t>TeaTime</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1113303393</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1097757129</t>
         </is>
       </c>
     </row>
@@ -3651,12 +3651,12 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>1144616337</t>
+          <t>1214072428</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>【クリアランスセール】 トーンアップ ブライトニング プログラム グルタチオン デイリー ホイップ バブル洗顔 泡洗顔 洗顔フォーム 洗顔料 保湿 ブライトニング Angels Liquid</t>
+          <t>[大容量,日本未入荷] ディープクレンジング ジェル CL 500ml + 120ml</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr"/>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Angel's Liquid</t>
+          <t>キールズ</t>
         </is>
       </c>
       <c r="G68" s="7" t="n">
-        <v>1200</v>
+        <v>6850</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>AngelsLiquid</t>
+          <t>supermoon</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1144616337</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214072428</t>
         </is>
       </c>
     </row>
@@ -3698,12 +3698,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>1210843857</t>
+          <t>1098240629</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Dr. Marci 米発酵セルタチオン 色素沈着・美白 メラノンクリーム, 1個</t>
+          <t>ピュア ハンドクリーム クリーンソープの香り 50ml</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr"/>
@@ -3714,28 +3714,28 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>dr.marci</t>
+          <t>Kundal</t>
         </is>
       </c>
       <c r="G69" s="7" t="n">
-        <v>3760</v>
+        <v>1079</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>바디/핸드/풋</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>drmarci</t>
+          <t>JfromKorea</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210843857</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1098240629</t>
         </is>
       </c>
     </row>
@@ -3745,12 +3745,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>1210837461</t>
+          <t>1197118760</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Dr. Marci 毛穴引き締め54% 皮脂コントロール クリーム, 1個</t>
+          <t>ボディローション 520ml 1+1セット ホワイトムスク 香り 大容量 保湿 ボディミルク ボディケア 乾燥肌 しっとり べたつかない ポンプ式 全身 潤い 韓国コスメ</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr"/>
@@ -3761,28 +3761,28 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>dr.marci</t>
+          <t>ブーケガルニ</t>
         </is>
       </c>
       <c r="G70" s="7" t="n">
-        <v>3760</v>
+        <v>3990</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>바디/핸드/풋</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>drmarci</t>
+          <t>k-essential</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1210837461</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1197118760</t>
         </is>
       </c>
     </row>
@@ -3792,12 +3792,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>1191430718</t>
+          <t>1209992767</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>ラボレブ ピーチマイクロバイオーム 78 PDRNトナー</t>
+          <t>足を洗おう 385ml フットシャンプー 泡 足の臭い 対策 角質 ケア 足洗い ソープ 爽快 バブル フットウォッシャー スプレー 足裏 洗浄 すっきり 潤い 保湿 フットケア ニオイ</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr"/>
@@ -3808,28 +3808,28 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Laboreve</t>
+          <t>オン・ザ・ボディー</t>
         </is>
       </c>
       <c r="G71" s="7" t="n">
-        <v>3300</v>
+        <v>1340</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>바디/핸드/풋</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>laboreve</t>
+          <t>k-essential</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191430718</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209992767</t>
         </is>
       </c>
     </row>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>1214263390</t>
+          <t>1214125215</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>【公式正規品】 バイオリフト HBA-X ブースタージェル 200mL (5本セット)</t>
+          <t>[トーン&amp;amp;スポット][正規品]トーン＆スポット リカバリークリーム 80ml（ボディ美白/色素沈着ケア/背中ニキビ/ツヤ肌/大容量）</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr"/>
@@ -3855,28 +3855,28 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>OCURA</t>
+          <t>Redence</t>
         </is>
       </c>
       <c r="G72" s="7" t="n">
-        <v>16415</v>
+        <v>6284</v>
       </c>
       <c r="H72" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>바디/핸드/풋</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>ocura</t>
+          <t>k-pick72811</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214263390</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214125215</t>
         </is>
       </c>
     </row>
@@ -3886,12 +3886,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>1214262100</t>
+          <t>1209488237</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>【公式正規品】 バイオリフト HBA-X ブースタージェル 200mL (2本セット)</t>
+          <t>[正規品][1+1+1]アクネ クレンジングフォーム 20ml／ニキビ機能性／緑茶水鎮静／ニキビ1位</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr"/>
@@ -3902,11 +3902,11 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>OCURA</t>
+          <t>ブランネイチャー</t>
         </is>
       </c>
       <c r="G73" s="7" t="n">
-        <v>7840</v>
+        <v>2924</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>0</v>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>ocura</t>
+          <t>k-pick72811</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214262100</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209488237</t>
         </is>
       </c>
     </row>
@@ -3933,12 +3933,12 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>1209394020</t>
+          <t>606150890</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>【公式正規品】 バイオリフト HBA-X ブースタージェル 200mL</t>
+          <t>PERIPERA Blur Pang ブラーパン バナナミルクブラー/ピュアミルクブラー/ピーチミルクブラー</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr"/>
@@ -3949,14 +3949,14 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>OCURA</t>
+          <t>ペリペラ</t>
         </is>
       </c>
       <c r="G74" s="7" t="n">
-        <v>4900</v>
+        <v>10000</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>ocura</t>
+          <t>fastbeauty</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1209394020</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=606150890</t>
         </is>
       </c>
     </row>
@@ -3980,12 +3980,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>1145834943</t>
+          <t>1146079054</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>薬用ローション スーパーセンシティブ EX 150ml 化粧水 セラミド 敏感肌 低刺激</t>
+          <t>プレミアムナチュレクレンジング PNクレンジング 250g</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr"/>
@@ -3996,14 +3996,14 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>ドクターシーラボ</t>
+          <t>ミューフル</t>
         </is>
       </c>
       <c r="G75" s="7" t="n">
-        <v>3480</v>
+        <v>12100</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>reraise</t>
+          <t>kenbi</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1145834943</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1146079054</t>
         </is>
       </c>
     </row>
@@ -4027,12 +4027,12 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>1161832347</t>
+          <t>1146192873</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>ナチュラルカバーファンデーション/ 極細毛ブラシ付/ スティック型/ 韓国化粧品</t>
+          <t>プレミアムナチュレローション PNローション 300mL</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr"/>
@@ -4043,28 +4043,28 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>オブジェ</t>
+          <t>ミューフル</t>
         </is>
       </c>
       <c r="G76" s="7" t="n">
-        <v>4950</v>
+        <v>9000</v>
       </c>
       <c r="H76" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>120000023</t>
+          <t>스킨케어</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>JUHACOSMETIC</t>
+          <t>kenbi</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1161832347</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1146192873</t>
         </is>
       </c>
     </row>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>1186959741</t>
+          <t>669602673</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>IHADA イハダ 薬用クリアローション 美白化粧水 180mL</t>
+          <t>アクア ラ ビュー 500ml</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr"/>
@@ -4090,14 +4090,14 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>イハダ</t>
+          <t>ギブアンドギブ</t>
         </is>
       </c>
       <c r="G77" s="7" t="n">
-        <v>1918</v>
+        <v>5500</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
@@ -4106,12 +4106,12 @@
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>medicareplus</t>
+          <t>kenbi</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1186959741</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=669602673</t>
         </is>
       </c>
     </row>
@@ -4121,12 +4121,12 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>1134404499</t>
+          <t>1211548014</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>ハード ジェル LTD メンズ 200ｇ</t>
+          <t>[NS 500 SB+SF] ソヘア ナリシングシャンプー ダメージケア 500g (1+1)</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr"/>
@@ -4137,11 +4137,11 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>ドアーズ</t>
+          <t>sohair</t>
         </is>
       </c>
       <c r="G78" s="7" t="n">
-        <v>2500</v>
+        <v>4150</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>0</v>
@@ -4153,12 +4153,12 @@
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>rbq</t>
+          <t>sohairofficial</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1134404499</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211548014</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>1190275225</t>
+          <t>1214907497</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>クーポンOK 　エニシーグローパック CLX フェ イシャルジェルパック　7回分</t>
+          <t>[RF100] モロッコアルガンオイル リファインド ダブルケア エッセンス</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr"/>
@@ -4184,28 +4184,28 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>エニシー</t>
+          <t>sohair</t>
         </is>
       </c>
       <c r="G79" s="7" t="n">
-        <v>19250</v>
+        <v>2850</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>andginc</t>
+          <t>sohairofficial</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1190275225</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214907497</t>
         </is>
       </c>
     </row>
@@ -4215,12 +4215,12 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>1166972261</t>
+          <t>1211802618</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>新 ヘーラールーノ ゴールドミルクローション(乳液) 120ml</t>
+          <t>[NS 500 SF] ソヘア ナリシングシャンプー ダメージケア スウィートフルーティ 500g</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr"/>
@@ -4231,28 +4231,28 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>大高酵素</t>
+          <t>sohair</t>
         </is>
       </c>
       <c r="G80" s="7" t="n">
-        <v>3564</v>
+        <v>2300</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>cosmesse</t>
+          <t>sohairofficial</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1166972261</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211802618</t>
         </is>
       </c>
     </row>
@@ -4262,12 +4262,12 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>1214463806</t>
+          <t>1211060520</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>[正規品] セメンザル ライトクリーム 100ml ㅣ 高保湿 · 肌バリアケア · 敏感肌向け · 韓国コスメ</t>
+          <t>[NS 1000 OG] ソヘア ナリシングシャンプー ダメージケア オリジナルハニーフラワー 1000g</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr"/>
@@ -4278,28 +4278,28 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>CONAPIDIL</t>
+          <t>sohair</t>
         </is>
       </c>
       <c r="G81" s="7" t="n">
-        <v>19590</v>
+        <v>3900</v>
       </c>
       <c r="H81" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>스킨케어</t>
+          <t>헤어</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>pinkri</t>
+          <t>sohairofficial</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214463806</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1211060520</t>
         </is>
       </c>
     </row>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>1023723980</t>
+          <t>1181403857</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>【国内正規品】 コスメデコルテ リポソーム アドバンスト リペアセラム 50ml 2個セット</t>
+          <t>リジュビネーションアンプル 30ml PDRN＋EGF 高濃度 敏感肌にも</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr"/>
@@ -4325,11 +4325,11 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>コスメデコルテ</t>
+          <t>ellie grace</t>
         </is>
       </c>
       <c r="G82" s="7" t="n">
-        <v>28600</v>
+        <v>6649</v>
       </c>
       <c r="H82" s="3" t="n">
         <v>0</v>
@@ -4341,17 +4341,1380 @@
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>decor_bote</t>
+          <t>elliegrace</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1023723980</t>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1181403857</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>1090183841</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>B.C.A.D.HOMME トータルエマルジョン 120ml オールインワン 化粧水</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr"/>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>ビーシーエーディー</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>gcb</t>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1090183841</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>1090331730</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>【お得な3本＋1本プレゼント】ナチュラルビューティセレクション スキャルプエッセンススプレー 180g 頭皮＆ボディ用美容液（リラックスグリーンティ）</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr"/>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>Natural Beauty Selection</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="n">
+        <v>7700</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>헤어</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>gcb</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1090331730</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>1090182799</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>ハードゼリー 300g</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr"/>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>ロレッタ</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>헤어</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>gcb</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1090182799</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="32" customHeight="1">
+      <c r="A86" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>1190724950</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>3種から1種選択 パフュームヘアオイル 80ml ヒノキ オスマントゥス ラピタ 10mlミニ付 エンジェルミュゲ 艶髪 保湿 ダメージケア 補修 スタイリング べたつかない 人気 ギフト 贈り物</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr"/>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>La'dor</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="n">
+        <v>4992</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>헤어</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>risingmother</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1190724950</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>1212757907</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>[26年リニューアル新型/クリーム2種セット] ビタトーニングカプセルクリームナイアシンアミド5%単一型+チューブ型 #無膜ビタカプセル トーンアップ 美白 毛穴ケア 保湿 ツヤ肌 ビタミンC 韓国</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr"/>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>ダルバ</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="n">
+        <v>9415</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>risingmother</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1212757907</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
+      <c r="A88" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>1052332764</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>エトトゥス アルガン シャンプー 1000ml+バオバブ ヘアパック 1000ml</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr"/>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>メディフラワー</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="n">
+        <v>3890</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>헤어</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>HNMALL</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1052332764</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="32" customHeight="1">
+      <c r="A89" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>1170300242</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>[25SS/新作](+リフィル30ml贈呈)PDRN ヒアルロン酸 カプセル 100 セラム 30ml+30ml 限定企画セット</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr"/>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>アヌア</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="n">
+        <v>4816</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>DreamWish</t>
+        </is>
+      </c>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1170300242</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="32" customHeight="1">
+      <c r="A90" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>1162181726</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>[25SS/New] PDRN ヒアルロン酸 カプセル100 セラムマスク 10枚入</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr"/>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>アヌア</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="n">
+        <v>2640</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>DreamWish</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1162181726</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="32" customHeight="1">
+      <c r="A91" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>1157418378</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>[25SS/New] ビタミンC 10% セラム 28ml+28ml</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr"/>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>LAYERLAB</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="n">
+        <v>10990</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>DreamWish</t>
+        </is>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1157418378</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>1200840903</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>PDRN ピンク カフェイン コラーゲン アイパッチ 60枚</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr"/>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="n">
+        <v>4438</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>busanjin</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1200840903</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="32" customHeight="1">
+      <c r="A93" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>1179523396</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>[25FW/New] TRICONIXトリコエックス 脱毛緩和 ボリューム シャンプー500ml #脱毛緩和 #頭皮ケア #特許成分 Trico-X #ピクスケリカ エキゾソーム原料 #ヒアルゾーム</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr"/>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>TRICO</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="n">
+        <v>5437</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>헤어</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>busanjin</t>
+        </is>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1179523396</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="32" customHeight="1">
+      <c r="A94" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>1201897263</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>トーンアンドスポット コレクター アンプル 30ml</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr"/>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>Redence</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="n">
+        <v>3290</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>siriya</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1201897263</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="32" customHeight="1">
+      <c r="A95" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>1201917236</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>スウェイリップデューイ 10color</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr"/>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>トゥークールフォースクール</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="n">
+        <v>1709</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>siriya</t>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1201917236</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="32" customHeight="1">
+      <c r="A96" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>1188484222</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>プロバイオダム コラーゲン リモデリング セラムゲル マスク 5+1枚贈呈 企画セット</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr"/>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>バイオヒールボ</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="n">
+        <v>2701</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>seoulglowpick</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1188484222</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="32" customHeight="1">
+      <c r="A97" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>1191658363</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>[新作]サンシビオ トナー 250ml</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr"/>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>ビオデルマ</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="n">
+        <v>3690</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>seoulglowpick</t>
+        </is>
+      </c>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191658363</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="32" customHeight="1">
+      <c r="A98" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>1191658129</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>[新作]ウルトラピュアセラム5.0% ナイアシンアミド 30ml</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr"/>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>キールズ</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="n">
+        <v>6505</v>
+      </c>
+      <c r="H98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>seoulglowpick</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191658129</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="32" customHeight="1">
+      <c r="A99" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>1198335587</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>[新作](+20mL追加贈呈)NMN テンションアップ サンセラム 50mL SPF50+ PA++++ NAD+ コラーゲン</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr"/>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>メイクプレム</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="n">
+        <v>3124</v>
+      </c>
+      <c r="H99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>UV케어</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>IrohaBeautyHub</t>
+        </is>
+      </c>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1198335587</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="32" customHeight="1">
+      <c r="A100" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>1191396172</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>[26SS/New] (1+1)ヒーロー マイファースト セーラムライト 155ml #脂性用万能基礎 #低分子ヒアルロン酸 #シカ #ティーツリー葉水 #抗酸化成分</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr"/>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>De:maf</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="n">
+        <v>5901</v>
+      </c>
+      <c r="H100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>trailblue2</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1191396172</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="32" customHeight="1">
+      <c r="A101" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>1214482617</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>[26SS/New]ビタAレチナルショット タイトニング デュアルクリーム 50ml #パンテノール #アズレン #レチナール0.05%</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr"/>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>celimax</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="n">
+        <v>3990</v>
+      </c>
+      <c r="H101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>trailblue2</t>
+        </is>
+      </c>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1214482617</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="32" customHeight="1">
+      <c r="A102" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>1137567849</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>アクアスクワラン モイスチャライジングクリーム 60ml</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr"/>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>エスネイチャー</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="n">
+        <v>1990</v>
+      </c>
+      <c r="H102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>45do</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1137567849</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="32" customHeight="1">
+      <c r="A103" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>1139845347</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>魔女工場 パンテトイン エッセンストナー 200ml / 2in1 化粧水 / 高保湿 / 鎮静ケア</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr"/>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>manyo</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="n">
+        <v>1990</v>
+      </c>
+      <c r="H103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>45do</t>
+        </is>
+      </c>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1139845347</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="32" customHeight="1">
+      <c r="A104" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>1164170834</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>[SKIN1004] (jL) Madagascar Centella Poremizing Light Gel Cream 75ml / マダガスカル センテラ ポアミゼーション ライトジェルクリー</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr"/>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="n">
+        <v>1899</v>
+      </c>
+      <c r="H104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>sweet-box</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1164170834</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="32" customHeight="1">
+      <c r="A105" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>1122653081</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>[SKIN1004] (bo) Madagascar Centella Probio-Cica Enrich Cream 50ml / マダガスカル センテラ プロビオ シカ エンリッチ クリーム</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr"/>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="n">
+        <v>2159</v>
+      </c>
+      <c r="H105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>sweet-box</t>
+        </is>
+      </c>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1122653081</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="32" customHeight="1">
+      <c r="A106" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>1072834879</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>[GRAYMELIN] (boL) トラブルソリューション スペシャルスキントナー 130ml / Trouble Solution Special Skin Toner 130ml</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr"/>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>グレイメリン</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="n">
+        <v>1599</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>sweet-box</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1072834879</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="32" customHeight="1">
+      <c r="A107" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>1067161790</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>[NEEDLY] (bo) Vita Cグロートーニングアンプル 30ml / Vita C Glow Toning Ampoule 30ml</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr"/>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>NEEDLY</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="n">
+        <v>1669</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>sweet-box</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1067161790</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="32" customHeight="1">
+      <c r="A108" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>1051833364</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>[Klairs] (jjL) Supple Preparation Unscented Toner 180ml / サプル プレパレーション 無香料トナー 180ml</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr"/>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>dear,Klairs</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="n">
+        <v>2089</v>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>sweet-box</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1051833364</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>1180394536</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Red Toner 100ml</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr"/>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>メディキューブ</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="n">
+        <v>2720</v>
+      </c>
+      <c r="H109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>Firstshopping</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1180394536</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>1176654205</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>プレミアムゴールドコラーゲントナー 180ml 化粧水</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr"/>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>エリシャコイ</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="n">
+        <v>3560</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>Firstshopping</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1176654205</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="32" customHeight="1">
+      <c r="A111" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>1073637375</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>コントロールA ティーツリーメント クレンジングフォーム 120ml 1EA</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr"/>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>일본어만</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>Dr.Jart+</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="n">
+        <v>1820</v>
+      </c>
+      <c r="H111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>스킨케어</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>DEARHOUR</t>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>https://m.qoo10.jp/gmkt.inc/Mobile/Goods/goods.aspx?goodscode=1073637375</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K82"/>
+  <autoFilter ref="A1:K111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>